--- a/data/meta_analysis/Cat meta-analysis - SMDs.xlsx
+++ b/data/meta_analysis/Cat meta-analysis - SMDs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wallacha@qut.edu.au/Documents/Research/Manuscripts/Death Star/Cats vs vertebrates/Datasets/Meta-analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA676D0-8E59-2B4B-AD6F-0DE8500BD060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952474F7-8F72-AF4E-9F74-2E7599FDB9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16740" xr2:uid="{6CF683D5-C8B8-0C42-9A59-7A45EEDDF505}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="16740" xr2:uid="{6CF683D5-C8B8-0C42-9A59-7A45EEDDF505}"/>
   </bookViews>
   <sheets>
     <sheet name="SMD" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="72">
   <si>
     <t>Effect_size_ID</t>
   </si>
@@ -218,7 +218,40 @@
     <t>Plots</t>
   </si>
   <si>
-    <t>Could also be defined short term</t>
+    <t>Inside-outside</t>
+  </si>
+  <si>
+    <t>Inside-outside abundance</t>
+  </si>
+  <si>
+    <t>ES_ARM</t>
+  </si>
+  <si>
+    <t>Peromyscus pseudocrinitus</t>
+  </si>
+  <si>
+    <t>Rodríguez-Moreno A, Arnaud G, Tershy BR (2007) Impacto de la eradicación del gato (Felis catus), en dos roedores endémicos de la Isla Coronados, Golfo de California, México. Acta Zoológica Mexicana, 23, 1-13.</t>
+  </si>
+  <si>
+    <t>Isla Coronados, Gulf of California</t>
+  </si>
+  <si>
+    <t>Before/after</t>
+  </si>
+  <si>
+    <t>Figure 2</t>
+  </si>
+  <si>
+    <t>47.96</t>
+  </si>
+  <si>
+    <t>22.48</t>
+  </si>
+  <si>
+    <t>Short-term abundance</t>
+  </si>
+  <si>
+    <t>unit_of_replication</t>
   </si>
 </sst>
 </file>
@@ -274,7 +307,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -297,6 +330,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDFF8D6"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -387,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -487,6 +526,24 @@
     </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -822,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CACEC97-16A3-304C-860E-29C0AFD6DD9D}">
-  <dimension ref="A1:AD451"/>
+  <dimension ref="A1:AN451"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" style="3" customWidth="1"/>
@@ -856,7 +913,7 @@
     <col min="30" max="16384" width="8.33203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:40" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -944,8 +1001,11 @@
       <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="AD1" s="3" t="s">
+        <v>71</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" s="13" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:40" s="13" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
@@ -1029,8 +1089,11 @@
       <c r="AC2" s="6" t="s">
         <v>40</v>
       </c>
+      <c r="AD2" s="13" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="3" spans="1:30" s="20" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:40" s="20" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
         <v>41</v>
       </c>
@@ -1112,8 +1175,11 @@
       <c r="AC3" s="16" t="s">
         <v>40</v>
       </c>
+      <c r="AD3" s="20" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="4" spans="1:30" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:40" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="21" t="s">
         <v>47</v>
       </c>
@@ -1197,8 +1263,11 @@
       <c r="AC4" s="12" t="s">
         <v>40</v>
       </c>
+      <c r="AD4" s="25" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="5" spans="1:30" s="20" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" s="20" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
         <v>50</v>
       </c>
@@ -1280,8 +1349,11 @@
       <c r="AC5" s="16" t="s">
         <v>40</v>
       </c>
+      <c r="AD5" s="20" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="6" spans="1:30" s="31" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" s="31" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="26" t="s">
         <v>52</v>
       </c>
@@ -1302,7 +1374,7 @@
         <v>136.53</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="I6" s="29"/>
       <c r="J6" s="29" t="s">
@@ -1363,22 +1435,107 @@
         <v>39</v>
       </c>
       <c r="AC6" s="28" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="AD6" s="28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:30" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:30" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:30" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:30" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:30" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:30" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:30" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:30" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:30" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:30" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:40" s="35" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="35">
+        <v>26.1191</v>
+      </c>
+      <c r="G7" s="35">
+        <v>-111.2756</v>
+      </c>
+      <c r="H7" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="K7" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="O7" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="P7" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q7" s="37">
+        <v>41.93</v>
+      </c>
+      <c r="R7" s="37">
+        <v>22.12</v>
+      </c>
+      <c r="S7" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="T7" s="39">
+        <v>1</v>
+      </c>
+      <c r="U7" s="39">
+        <v>1</v>
+      </c>
+      <c r="V7" s="39">
+        <v>9</v>
+      </c>
+      <c r="W7" s="39">
+        <v>3</v>
+      </c>
+      <c r="X7" s="39">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="39">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="35">
+        <v>9</v>
+      </c>
+      <c r="AA7" s="35">
+        <v>3</v>
+      </c>
+      <c r="AB7" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC7" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD7" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="AM7" s="34"/>
+      <c r="AN7" s="34"/>
+    </row>
+    <row r="8" spans="1:40" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:40" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:40" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:40" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:40" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:40" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:40" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:40" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:40" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" spans="16:17" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="18" spans="16:17" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="19" spans="16:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">

--- a/data/meta_analysis/Cat meta-analysis - SMDs.xlsx
+++ b/data/meta_analysis/Cat meta-analysis - SMDs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wallacha@qut.edu.au/Documents/Research/Manuscripts/Death Star/Cats vs vertebrates/Datasets/Meta-analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952474F7-8F72-AF4E-9F74-2E7599FDB9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A35265-016F-F544-9572-E8AF838541A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="16740" xr2:uid="{6CF683D5-C8B8-0C42-9A59-7A45EEDDF505}"/>
+    <workbookView xWindow="560" yWindow="660" windowWidth="29400" windowHeight="16740" xr2:uid="{6CF683D5-C8B8-0C42-9A59-7A45EEDDF505}"/>
   </bookViews>
   <sheets>
     <sheet name="SMD" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="89">
   <si>
     <t>Effect_size_ID</t>
   </si>
@@ -252,6 +252,57 @@
   </si>
   <si>
     <t>unit_of_replication</t>
+  </si>
+  <si>
+    <t>ES_43</t>
+  </si>
+  <si>
+    <t>Procellaria cinerea</t>
+  </si>
+  <si>
+    <t>Dilley, B.J., Schoombie, S., Stevens, K., Davies, D., Perold, V., Osborne, A., Schoombie, J., Brink, C.W., Carpenter-Kling, T. and Ryan, P.G., 2018. Mouse predation affects breeding success of burrow-nesting petrels at sub-Antarctic Marion Island. Antarctic Science, 30(2), pp.93-104.</t>
+  </si>
+  <si>
+    <t>Marion Island</t>
+  </si>
+  <si>
+    <t>Breeding success (percent)</t>
+  </si>
+  <si>
+    <t>Reproduction</t>
+  </si>
+  <si>
+    <t>Reproduction before-after eradication</t>
+  </si>
+  <si>
+    <t>ES_37</t>
+  </si>
+  <si>
+    <t>Procellaria aequinoctialis</t>
+  </si>
+  <si>
+    <t>ES_47a</t>
+  </si>
+  <si>
+    <t>Marks, J.S. and Redmond, R.L., 1994. Conservation problems and research needs for Bristle-thighed Curlews Numenius tahitiensis on their wintering grounds. Bird Conservation International, 4(4), pp.329-341.</t>
+  </si>
+  <si>
+    <t>Howland</t>
+  </si>
+  <si>
+    <t>Baker</t>
+  </si>
+  <si>
+    <t>ES_47b</t>
+  </si>
+  <si>
+    <t>Surveys</t>
+  </si>
+  <si>
+    <t>Abundance before-after eradication</t>
+  </si>
+  <si>
+    <t>Table 2</t>
   </si>
 </sst>
 </file>
@@ -261,7 +312,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -283,19 +334,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
@@ -307,7 +345,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -320,26 +358,8 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF8D5"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF8D6"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -349,76 +369,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFA5A5A5"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFA5A5A5"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFA5A5A5"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA5A5A5"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA5A5A5"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA5A5A5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFA5A5A5"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA5A5A5"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA5A5A5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA5A5A5"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFA5A5A5"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA5A5A5"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA5A5A5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA5A5A5"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFA5A5A5"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA5A5A5"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -426,124 +386,61 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -882,655 +779,997 @@
   <dimension ref="A1:AN451"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11" style="3" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="54.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="29.1640625" style="3" customWidth="1"/>
-    <col min="6" max="7" width="11.1640625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5" style="3" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14" style="3" customWidth="1"/>
-    <col min="13" max="13" width="16.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5" style="3" customWidth="1"/>
-    <col min="15" max="15" width="15" style="3" customWidth="1"/>
-    <col min="16" max="16" width="21.1640625" style="32" customWidth="1"/>
-    <col min="17" max="17" width="21.6640625" style="32" customWidth="1"/>
-    <col min="18" max="18" width="20.6640625" style="32" customWidth="1"/>
-    <col min="19" max="19" width="21.1640625" style="32" customWidth="1"/>
-    <col min="20" max="20" width="28.6640625" style="3" customWidth="1"/>
-    <col min="21" max="21" width="29.1640625" style="3" customWidth="1"/>
-    <col min="22" max="22" width="26.33203125" style="3" customWidth="1"/>
-    <col min="23" max="23" width="26.83203125" style="3" customWidth="1"/>
-    <col min="24" max="24" width="25.6640625" style="3" customWidth="1"/>
-    <col min="25" max="25" width="26.33203125" style="3" customWidth="1"/>
-    <col min="26" max="26" width="28.5" style="3" customWidth="1"/>
-    <col min="27" max="27" width="29" style="3" customWidth="1"/>
-    <col min="28" max="28" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="32.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="8.33203125" style="3"/>
+    <col min="1" max="1" width="11" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="54.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.1640625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="11.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14" style="1" customWidth="1"/>
+    <col min="13" max="13" width="16.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5" style="1" customWidth="1"/>
+    <col min="15" max="15" width="15" style="1" customWidth="1"/>
+    <col min="16" max="16" width="21.1640625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="21.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="20.6640625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="21.1640625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="28.6640625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="29.1640625" style="1" customWidth="1"/>
+    <col min="22" max="22" width="26.33203125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="26.83203125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="25.6640625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="26.33203125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="28.5" style="1" customWidth="1"/>
+    <col min="27" max="27" width="29" style="1" customWidth="1"/>
+    <col min="28" max="28" width="14.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="32.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="8.33203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="6" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6" t="s">
+      <c r="D2" s="9"/>
+      <c r="E2" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="10">
         <v>-47.010300000000001</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="10">
         <v>167.8272</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7" t="s">
+      <c r="I2" s="10"/>
+      <c r="J2" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="11">
         <v>7.6</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="Q2" s="11">
         <v>4.3</v>
       </c>
-      <c r="R2" s="10">
+      <c r="R2" s="12">
         <v>5.8805065379486772</v>
       </c>
-      <c r="S2" s="10">
+      <c r="S2" s="12">
         <v>0.72020830320123297</v>
       </c>
-      <c r="T2" s="7">
+      <c r="T2" s="10">
         <v>7</v>
       </c>
-      <c r="U2" s="7">
+      <c r="U2" s="10">
         <v>3</v>
       </c>
-      <c r="V2" s="11">
-        <v>1</v>
-      </c>
-      <c r="W2" s="11">
-        <v>1</v>
-      </c>
-      <c r="X2" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="11">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="7">
+      <c r="V2" s="10">
+        <v>1</v>
+      </c>
+      <c r="W2" s="10">
+        <v>1</v>
+      </c>
+      <c r="X2" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="10">
         <v>7</v>
       </c>
-      <c r="AA2" s="7">
+      <c r="AA2" s="10">
         <v>3</v>
       </c>
-      <c r="AB2" s="12" t="s">
+      <c r="AB2" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="AC2" s="6" t="s">
+      <c r="AC2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AD2" s="13" t="s">
+      <c r="AD2" s="10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:40" s="20" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="s">
+    <row r="3" spans="1:40" s="13" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16" t="s">
+      <c r="D3" s="9"/>
+      <c r="E3" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="17">
+      <c r="F3" s="10">
         <v>-18.75</v>
       </c>
-      <c r="G3" s="17">
+      <c r="G3" s="10">
         <v>-141.76</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="18" t="s">
+      <c r="I3" s="10"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="L3" s="17" t="s">
+      <c r="L3" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="M3" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="N3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="O3" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="12">
         <v>7.5083333333333329</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="12">
         <v>0.01</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="12">
         <v>1.4142135623730951E-2</v>
       </c>
-      <c r="S3" s="19">
+      <c r="S3" s="12">
         <v>18.235267386760924</v>
       </c>
-      <c r="T3" s="17">
+      <c r="T3" s="10">
         <v>2</v>
       </c>
-      <c r="U3" s="17">
+      <c r="U3" s="10">
         <v>6</v>
       </c>
-      <c r="V3" s="17">
-        <v>1</v>
-      </c>
-      <c r="W3" s="17">
-        <v>1</v>
-      </c>
-      <c r="X3" s="17">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="17">
+      <c r="V3" s="10">
+        <v>1</v>
+      </c>
+      <c r="W3" s="10">
+        <v>1</v>
+      </c>
+      <c r="X3" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="10">
         <v>2</v>
       </c>
-      <c r="AA3" s="17">
+      <c r="AA3" s="10">
         <v>6</v>
       </c>
-      <c r="AB3" s="16" t="s">
+      <c r="AB3" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="AC3" s="16" t="s">
+      <c r="AC3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AD3" s="20" t="s">
+      <c r="AD3" s="10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:40" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="21" t="s">
+    <row r="4" spans="1:40" s="13" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12" t="s">
+      <c r="D4" s="9"/>
+      <c r="E4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="10">
         <v>-18.75</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="10">
         <v>-141.76</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="12" t="s">
+      <c r="I4" s="10"/>
+      <c r="J4" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="23" t="s">
+      <c r="K4" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="12" t="s">
+      <c r="N4" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="P4" s="24">
+      <c r="P4" s="12">
         <v>0.36299999999999999</v>
       </c>
-      <c r="Q4" s="24">
+      <c r="Q4" s="12">
         <v>0</v>
       </c>
-      <c r="R4" s="24">
+      <c r="R4" s="12">
         <v>0.88998127321122145</v>
       </c>
-      <c r="S4" s="24">
+      <c r="S4" s="12">
         <v>0</v>
       </c>
-      <c r="T4" s="11">
+      <c r="T4" s="10">
         <v>2</v>
       </c>
-      <c r="U4" s="11">
+      <c r="U4" s="10">
         <v>6</v>
       </c>
-      <c r="V4" s="11">
-        <v>1</v>
-      </c>
-      <c r="W4" s="11">
-        <v>1</v>
-      </c>
-      <c r="X4" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="11">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="11">
+      <c r="V4" s="10">
+        <v>1</v>
+      </c>
+      <c r="W4" s="10">
+        <v>1</v>
+      </c>
+      <c r="X4" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="10">
         <v>2</v>
       </c>
-      <c r="AA4" s="11">
+      <c r="AA4" s="10">
         <v>6</v>
       </c>
-      <c r="AB4" s="12" t="s">
+      <c r="AB4" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="AC4" s="12" t="s">
+      <c r="AC4" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AD4" s="25" t="s">
+      <c r="AD4" s="10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:40" s="20" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:40" s="13" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16" t="s">
+      <c r="D5" s="9"/>
+      <c r="E5" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="10">
         <v>-18.75</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="10">
         <v>-141.76</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="17"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="18" t="s">
+      <c r="I5" s="10"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="L5" s="17" t="s">
+      <c r="L5" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="M5" s="16" t="s">
+      <c r="M5" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="N5" s="16" t="s">
+      <c r="N5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="O5" s="17" t="s">
+      <c r="O5" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="P5" s="19">
+      <c r="P5" s="12">
         <v>2.4</v>
       </c>
-      <c r="Q5" s="19">
+      <c r="Q5" s="12">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="R5" s="19">
+      <c r="R5" s="12">
         <v>4.9497474683058332E-2</v>
       </c>
-      <c r="S5" s="19">
+      <c r="S5" s="12">
         <v>3.4721693507085742</v>
       </c>
-      <c r="T5" s="17">
+      <c r="T5" s="10">
         <v>2</v>
       </c>
-      <c r="U5" s="17">
+      <c r="U5" s="10">
         <v>6</v>
       </c>
-      <c r="V5" s="17">
-        <v>1</v>
-      </c>
-      <c r="W5" s="17">
-        <v>1</v>
-      </c>
-      <c r="X5" s="17">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="17">
+      <c r="V5" s="10">
+        <v>1</v>
+      </c>
+      <c r="W5" s="10">
+        <v>1</v>
+      </c>
+      <c r="X5" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="10">
         <v>2</v>
       </c>
-      <c r="AA5" s="17">
+      <c r="AA5" s="10">
         <v>6</v>
       </c>
-      <c r="AB5" s="16" t="s">
+      <c r="AB5" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="AC5" s="16" t="s">
+      <c r="AC5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AD5" s="20" t="s">
+      <c r="AD5" s="10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:40" s="31" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26" t="s">
+    <row r="6" spans="1:40" s="13" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28" t="s">
+      <c r="D6" s="9"/>
+      <c r="E6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="10">
         <v>-30.29</v>
       </c>
-      <c r="G6" s="29">
+      <c r="G6" s="10">
         <v>136.53</v>
       </c>
-      <c r="H6" s="29" t="s">
+      <c r="H6" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29" t="s">
+      <c r="I6" s="10"/>
+      <c r="J6" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="K6" s="28" t="s">
+      <c r="K6" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L6" s="29" t="s">
+      <c r="L6" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="M6" s="28" t="s">
+      <c r="M6" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="N6" s="28" t="s">
+      <c r="N6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="29" t="s">
+      <c r="O6" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="P6" s="30">
+      <c r="P6" s="12">
         <v>38.869999999999997</v>
       </c>
-      <c r="Q6" s="30">
+      <c r="Q6" s="12">
         <v>1.03</v>
       </c>
-      <c r="R6" s="30">
+      <c r="R6" s="12">
         <v>29.11</v>
       </c>
-      <c r="S6" s="30">
+      <c r="S6" s="12">
         <v>1.26</v>
       </c>
-      <c r="T6" s="29">
+      <c r="T6" s="10">
         <v>40</v>
       </c>
-      <c r="U6" s="29">
+      <c r="U6" s="10">
         <v>15</v>
       </c>
-      <c r="V6" s="29">
-        <v>1</v>
-      </c>
-      <c r="W6" s="29">
-        <v>1</v>
-      </c>
-      <c r="X6" s="29">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="29">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="29">
+      <c r="V6" s="10">
+        <v>1</v>
+      </c>
+      <c r="W6" s="10">
+        <v>1</v>
+      </c>
+      <c r="X6" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="10">
         <v>40</v>
       </c>
-      <c r="AA6" s="29">
+      <c r="AA6" s="10">
         <v>15</v>
       </c>
-      <c r="AB6" s="28" t="s">
+      <c r="AB6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="AC6" s="28" t="s">
+      <c r="AC6" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="AD6" s="28" t="s">
+      <c r="AD6" s="9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:40" s="35" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="38" t="s">
+    <row r="7" spans="1:40" s="13" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34" t="s">
+      <c r="D7" s="9"/>
+      <c r="E7" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="10">
         <v>26.1191</v>
       </c>
-      <c r="G7" s="35">
+      <c r="G7" s="10">
         <v>-111.2756</v>
       </c>
-      <c r="H7" s="35" t="s">
+      <c r="H7" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="K7" s="35" t="s">
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L7" s="17" t="s">
+      <c r="L7" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="M7" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="N7" s="16" t="s">
+      <c r="N7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="O7" s="35" t="s">
+      <c r="O7" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="P7" s="36" t="s">
+      <c r="P7" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="Q7" s="37">
+      <c r="Q7" s="11">
         <v>41.93</v>
       </c>
-      <c r="R7" s="37">
+      <c r="R7" s="11">
         <v>22.12</v>
       </c>
-      <c r="S7" s="36" t="s">
+      <c r="S7" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="T7" s="39">
-        <v>1</v>
-      </c>
-      <c r="U7" s="39">
-        <v>1</v>
-      </c>
-      <c r="V7" s="39">
+      <c r="T7" s="15">
+        <v>1</v>
+      </c>
+      <c r="U7" s="15">
+        <v>1</v>
+      </c>
+      <c r="V7" s="15">
         <v>9</v>
       </c>
-      <c r="W7" s="39">
+      <c r="W7" s="15">
         <v>3</v>
       </c>
-      <c r="X7" s="39">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="39">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="35">
+      <c r="X7" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="15">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="10">
         <v>9</v>
       </c>
-      <c r="AA7" s="35">
+      <c r="AA7" s="10">
         <v>3</v>
       </c>
-      <c r="AB7" s="35" t="s">
+      <c r="AB7" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AC7" s="35" t="s">
+      <c r="AC7" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="AD7" s="35" t="s">
+      <c r="AD7" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="AM7" s="34"/>
-      <c r="AN7" s="34"/>
+      <c r="AM7" s="16"/>
+      <c r="AN7" s="16"/>
     </row>
-    <row r="8" spans="1:40" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:40" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:40" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:40" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:40" s="13" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="10">
+        <v>-46.875459999999997</v>
+      </c>
+      <c r="G8" s="10">
+        <v>37.858539999999998</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="P8" s="11">
+        <v>30.66</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>15.93</v>
+      </c>
+      <c r="R8" s="11">
+        <v>20.329999999999998</v>
+      </c>
+      <c r="S8" s="11">
+        <v>27.59</v>
+      </c>
+      <c r="T8" s="10">
+        <v>1</v>
+      </c>
+      <c r="U8" s="10">
+        <v>1</v>
+      </c>
+      <c r="V8" s="10">
+        <v>5</v>
+      </c>
+      <c r="W8" s="10">
+        <v>3</v>
+      </c>
+      <c r="X8" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="10">
+        <v>5</v>
+      </c>
+      <c r="AA8" s="10">
+        <v>3</v>
+      </c>
+      <c r="AB8" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC8" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD8" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:40" s="13" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" s="10">
+        <v>-46.876399999999997</v>
+      </c>
+      <c r="G9" s="10">
+        <v>37.859099999999998</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="P9" s="11">
+        <v>55.5</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>48.63</v>
+      </c>
+      <c r="R9" s="11">
+        <v>18.170000000000002</v>
+      </c>
+      <c r="S9" s="11">
+        <v>14.73</v>
+      </c>
+      <c r="T9" s="10">
+        <v>1</v>
+      </c>
+      <c r="U9" s="10">
+        <v>1</v>
+      </c>
+      <c r="V9" s="10">
+        <v>9</v>
+      </c>
+      <c r="W9" s="10">
+        <v>3</v>
+      </c>
+      <c r="X9" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="10">
+        <v>9</v>
+      </c>
+      <c r="AA9" s="10">
+        <v>3</v>
+      </c>
+      <c r="AB9" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC9" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD9" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:40" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="6">
+        <v>-4.5</v>
+      </c>
+      <c r="G10" s="6">
+        <v>-172</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="O10" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="P10" s="7">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>2.83</v>
+      </c>
+      <c r="R10" s="7">
+        <v>14.47</v>
+      </c>
+      <c r="S10" s="7">
+        <v>5.07</v>
+      </c>
+      <c r="T10" s="10">
+        <v>1</v>
+      </c>
+      <c r="U10" s="10">
+        <v>1</v>
+      </c>
+      <c r="V10" s="6">
+        <v>3</v>
+      </c>
+      <c r="W10" s="6">
+        <v>6</v>
+      </c>
+      <c r="X10" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="6">
+        <v>3</v>
+      </c>
+      <c r="AA10" s="6">
+        <v>6</v>
+      </c>
+      <c r="AB10" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC10" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD10" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:40" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="6">
+        <v>-4.5</v>
+      </c>
+      <c r="G11" s="6">
+        <v>-172</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="O11" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="P11" s="7">
+        <v>15.71</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="R11" s="7">
+        <v>7.76</v>
+      </c>
+      <c r="S11" s="7">
+        <v>3.54</v>
+      </c>
+      <c r="T11" s="10">
+        <v>1</v>
+      </c>
+      <c r="U11" s="10">
+        <v>1</v>
+      </c>
+      <c r="V11" s="6">
+        <v>7</v>
+      </c>
+      <c r="W11" s="6">
+        <v>2</v>
+      </c>
+      <c r="X11" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="6">
+        <v>7</v>
+      </c>
+      <c r="AA11" s="6">
+        <v>2</v>
+      </c>
+      <c r="AB11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC11" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD11" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
     <row r="12" spans="1:40" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="13" spans="1:40" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:40" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -1539,12 +1778,12 @@
     <row r="17" spans="16:17" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="18" spans="16:17" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="19" spans="16:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="P19" s="33"/>
-      <c r="Q19" s="33"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
     </row>
     <row r="20" spans="16:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="P20" s="33"/>
-      <c r="Q20" s="33"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
     </row>
     <row r="21" spans="16:17" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="16:17" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
